--- a/stacks/ledger/economy.xlsx
+++ b/stacks/ledger/economy.xlsx
@@ -720,7 +720,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>{&gt;= {econ.total_earned} 1500}</t>
+          <t>{{econ.total_earned} &gt;= 1500}</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>{&gt;= {econ.total_earned} 4000}</t>
+          <t>{{econ.total_earned} &gt;= 4000}</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{&gt;= {econ.total_earned} 10000}</t>
+          <t>{{econ.total_earned} &gt;= 10000}</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>{&gt;= {econ.total_earned} 25000}</t>
+          <t>{{econ.total_earned} &gt;= 25000}</t>
         </is>
       </c>
     </row>
